--- a/research/traditional_assets/database/data/hong_kong/hong_kong_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0281</v>
+        <v>-0.00073</v>
       </c>
       <c r="E2">
-        <v>0.0442</v>
+        <v>-0.00041</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>64.7</v>
+        <v>56.5</v>
       </c>
       <c r="L2">
-        <v>0.3385661957090529</v>
+        <v>0.3277262180974478</v>
       </c>
       <c r="M2">
-        <v>21.2</v>
+        <v>28</v>
       </c>
       <c r="N2">
-        <v>0.05790767549849767</v>
+        <v>0.0825228411435308</v>
       </c>
       <c r="O2">
-        <v>0.3276661514683153</v>
+        <v>0.495575221238938</v>
       </c>
       <c r="P2">
-        <v>21.2</v>
+        <v>28</v>
       </c>
       <c r="Q2">
-        <v>0.05790767549849767</v>
+        <v>0.0825228411435308</v>
       </c>
       <c r="R2">
-        <v>0.3276661514683153</v>
+        <v>0.495575221238938</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>771.9</v>
+        <v>546.6</v>
       </c>
       <c r="V2">
-        <v>2.108440316853319</v>
+        <v>1.610963748894783</v>
       </c>
       <c r="W2">
-        <v>0.06217566788391313</v>
+        <v>0.05182059983490783</v>
       </c>
       <c r="X2">
-        <v>0.06090212079199641</v>
+        <v>0.07726600290397415</v>
       </c>
       <c r="Y2">
-        <v>0.001273547091916724</v>
+        <v>-0.02544540306906632</v>
       </c>
       <c r="Z2">
-        <v>0.8352272727272728</v>
+        <v>0.9723632261703328</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04712231232387284</v>
+        <v>0.06497362057758162</v>
       </c>
       <c r="AC2">
-        <v>-0.04712231232387284</v>
+        <v>-0.06497362057758162</v>
       </c>
       <c r="AD2">
-        <v>216.2</v>
+        <v>215.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>216.2</v>
+        <v>215.5</v>
       </c>
       <c r="AG2">
-        <v>-555.7</v>
+        <v>-331.1</v>
       </c>
       <c r="AH2">
-        <v>0.3712862785505753</v>
+        <v>0.3884282624369143</v>
       </c>
       <c r="AI2">
-        <v>0.1654802908534252</v>
+        <v>0.1632946881867091</v>
       </c>
       <c r="AJ2">
-        <v>2.93090717299578</v>
+        <v>-40.37804878048787</v>
       </c>
       <c r="AK2">
-        <v>-1.039468761690984</v>
+        <v>-0.4282757728625016</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0281</v>
+        <v>-0.00073</v>
       </c>
       <c r="E3">
-        <v>0.0442</v>
+        <v>-0.00041</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>64.7</v>
+        <v>56.5</v>
       </c>
       <c r="L3">
-        <v>0.3385661957090529</v>
+        <v>0.3277262180974478</v>
       </c>
       <c r="M3">
-        <v>21.2</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>0.05790767549849767</v>
+        <v>0.0825228411435308</v>
       </c>
       <c r="O3">
-        <v>0.3276661514683153</v>
+        <v>0.495575221238938</v>
       </c>
       <c r="P3">
-        <v>21.2</v>
+        <v>28</v>
       </c>
       <c r="Q3">
-        <v>0.05790767549849767</v>
+        <v>0.0825228411435308</v>
       </c>
       <c r="R3">
-        <v>0.3276661514683153</v>
+        <v>0.495575221238938</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>771.9</v>
+        <v>546.6</v>
       </c>
       <c r="V3">
-        <v>2.108440316853319</v>
+        <v>1.610963748894783</v>
       </c>
       <c r="W3">
-        <v>0.06217566788391313</v>
+        <v>0.05182059983490783</v>
       </c>
       <c r="X3">
-        <v>0.06090212079199641</v>
+        <v>0.07726600290397415</v>
       </c>
       <c r="Y3">
-        <v>0.001273547091916724</v>
+        <v>-0.02544540306906632</v>
       </c>
       <c r="Z3">
-        <v>0.8352272727272728</v>
+        <v>0.9723632261703328</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04712231232387284</v>
+        <v>0.06497362057758162</v>
       </c>
       <c r="AC3">
-        <v>-0.04712231232387284</v>
+        <v>-0.06497362057758162</v>
       </c>
       <c r="AD3">
-        <v>216.2</v>
+        <v>215.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>216.2</v>
+        <v>215.5</v>
       </c>
       <c r="AG3">
-        <v>-555.7</v>
+        <v>-331.1</v>
       </c>
       <c r="AH3">
-        <v>0.3712862785505753</v>
+        <v>0.3884282624369143</v>
       </c>
       <c r="AI3">
-        <v>0.1654802908534252</v>
+        <v>0.1632946881867091</v>
       </c>
       <c r="AJ3">
-        <v>2.93090717299578</v>
+        <v>-40.37804878048787</v>
       </c>
       <c r="AK3">
-        <v>-1.039468761690984</v>
+        <v>-0.4282757728625016</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00073</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.00041</v>
+        <v>-0.139</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>56.5</v>
+        <v>31.8</v>
       </c>
       <c r="L2">
-        <v>0.3277262180974478</v>
+        <v>0.2166212534059945</v>
       </c>
       <c r="M2">
-        <v>28</v>
+        <v>22.4</v>
       </c>
       <c r="N2">
-        <v>0.0825228411435308</v>
+        <v>0.09898365002209455</v>
       </c>
       <c r="O2">
-        <v>0.495575221238938</v>
+        <v>0.7044025157232704</v>
       </c>
       <c r="P2">
-        <v>28</v>
+        <v>22.4</v>
       </c>
       <c r="Q2">
-        <v>0.0825228411435308</v>
+        <v>0.09898365002209455</v>
       </c>
       <c r="R2">
-        <v>0.495575221238938</v>
+        <v>0.7044025157232704</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>546.6</v>
+        <v>267.1</v>
       </c>
       <c r="V2">
-        <v>1.610963748894783</v>
+        <v>1.180291648254529</v>
       </c>
       <c r="W2">
-        <v>0.05182059983490783</v>
+        <v>0.02879913059228401</v>
       </c>
       <c r="X2">
-        <v>0.07726600290397415</v>
+        <v>0.06709563623937781</v>
       </c>
       <c r="Y2">
-        <v>-0.02544540306906632</v>
+        <v>-0.0382965056470938</v>
       </c>
       <c r="Z2">
-        <v>0.9723632261703328</v>
+        <v>0.3498570066730219</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06497362057758162</v>
+        <v>0.05560330008916829</v>
       </c>
       <c r="AC2">
-        <v>-0.06497362057758162</v>
+        <v>-0.05560330008916829</v>
       </c>
       <c r="AD2">
-        <v>215.5</v>
+        <v>207.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>215.5</v>
+        <v>207.4</v>
       </c>
       <c r="AG2">
-        <v>-331.1</v>
+        <v>-59.70000000000002</v>
       </c>
       <c r="AH2">
-        <v>0.3884282624369143</v>
+        <v>0.4782107447544385</v>
       </c>
       <c r="AI2">
-        <v>0.1632946881867091</v>
+        <v>0.1565992147387496</v>
       </c>
       <c r="AJ2">
-        <v>-40.37804878048787</v>
+        <v>-0.3583433373349341</v>
       </c>
       <c r="AK2">
-        <v>-0.4282757728625016</v>
+        <v>-0.0564645795895205</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00073</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="E3">
-        <v>-0.00041</v>
+        <v>-0.139</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>56.5</v>
+        <v>31.8</v>
       </c>
       <c r="L3">
-        <v>0.3277262180974478</v>
+        <v>0.2166212534059945</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>22.4</v>
       </c>
       <c r="N3">
-        <v>0.0825228411435308</v>
+        <v>0.09898365002209455</v>
       </c>
       <c r="O3">
-        <v>0.495575221238938</v>
+        <v>0.7044025157232704</v>
       </c>
       <c r="P3">
-        <v>28</v>
+        <v>22.4</v>
       </c>
       <c r="Q3">
-        <v>0.0825228411435308</v>
+        <v>0.09898365002209455</v>
       </c>
       <c r="R3">
-        <v>0.495575221238938</v>
+        <v>0.7044025157232704</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>546.6</v>
+        <v>267.1</v>
       </c>
       <c r="V3">
-        <v>1.610963748894783</v>
+        <v>1.180291648254529</v>
       </c>
       <c r="W3">
-        <v>0.05182059983490783</v>
+        <v>0.02879913059228401</v>
       </c>
       <c r="X3">
-        <v>0.07726600290397415</v>
+        <v>0.06709563623937781</v>
       </c>
       <c r="Y3">
-        <v>-0.02544540306906632</v>
+        <v>-0.0382965056470938</v>
       </c>
       <c r="Z3">
-        <v>0.9723632261703328</v>
+        <v>0.3498570066730219</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06497362057758162</v>
+        <v>0.05560330008916829</v>
       </c>
       <c r="AC3">
-        <v>-0.06497362057758162</v>
+        <v>-0.05560330008916829</v>
       </c>
       <c r="AD3">
-        <v>215.5</v>
+        <v>207.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>215.5</v>
+        <v>207.4</v>
       </c>
       <c r="AG3">
-        <v>-331.1</v>
+        <v>-59.70000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.3884282624369143</v>
+        <v>0.4782107447544385</v>
       </c>
       <c r="AI3">
-        <v>0.1632946881867091</v>
+        <v>0.1565992147387496</v>
       </c>
       <c r="AJ3">
-        <v>-40.37804878048787</v>
+        <v>-0.3583433373349341</v>
       </c>
       <c r="AK3">
-        <v>-0.4282757728625016</v>
+        <v>-0.0564645795895205</v>
       </c>
       <c r="AL3">
         <v>0</v>
